--- a/ExcelRAddIn/Tests/Logistic Regression.xlsx
+++ b/ExcelRAddIn/Tests/Logistic Regression.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EAC1CC-5169-4A75-AB2A-6160273C547B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8712CE2-EAFE-469F-AF64-330092D8A8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{41A9D9A1-511C-404C-ADF4-02DA0BD5CB59}"/>
   </bookViews>
@@ -284,9 +284,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -324,7 +324,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -430,7 +430,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -572,7 +572,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84D8FD8F-E87F-4D9A-A59C-1156588135E9}">
-  <dimension ref="B2:D18"/>
+  <dimension ref="B2:D21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -627,87 +627,102 @@
         <v>4</v>
       </c>
       <c r="D2" t="str" cm="1">
-        <f t="array" ref="D2:D18">_xll.RScript.Evaluate(B2)</f>
-        <v>lubridate</v>
+        <f t="array" ref="D2:D21">_xll.RScript.Evaluate(B2)</f>
+        <v>reticulate</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D3" t="str">
-        <v>forcats</v>
+        <v>ggthemes</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D4" t="str">
-        <v>stringr</v>
+        <v>forecast</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D5" t="str">
-        <v>dplyr</v>
+        <v>lubridate</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D6" t="str">
-        <v>purrr</v>
+        <v>forcats</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D7" t="str">
-        <v>readr</v>
+        <v>stringr</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D8" t="str">
-        <v>tidyr</v>
+        <v>dplyr</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D9" t="str">
-        <v>tibble</v>
+        <v>purrr</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D10" t="str">
-        <v>ggplot2</v>
+        <v>readr</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D11" t="str">
-        <v>tidyverse</v>
+        <v>tidyr</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D12" t="str">
-        <v>stats</v>
+        <v>tibble</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D13" t="str">
-        <v>graphics</v>
+        <v>ggplot2</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D14" t="str">
-        <v>grDevices</v>
+        <v>tidyverse</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D15" t="str">
-        <v>utils</v>
+        <v>stats</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D16" t="str">
-        <v>datasets</v>
+        <v>graphics</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D17" t="str">
-        <v>methods</v>
+        <v>grDevices</v>
       </c>
     </row>
     <row r="18" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D18" t="str">
+        <v>utils</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D19" t="str">
+        <v>datasets</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D20" t="str">
+        <v>methods</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D21" t="str">
         <v>base</v>
       </c>
     </row>
